--- a/results/gateway_benchmark_workbook.xlsx
+++ b/results/gateway_benchmark_workbook.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 20:51 UTC</t>
+          <t>2026-08-19 22:54 UTC</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NOT PRESENT - every timing cell below is empty and awaiting a live run. Run scripts/run_all.py against real sandboxes, then re-run scripts/build_workbook.py to fold the numbers in.</t>
+          <t>NOT PRESENT - every timing cell below is empty and awaiting a live run. Export measured results from BuraPay as JSON, then re-run scripts/build_workbook.py to fold the numbers in.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Empty by design. Run scripts/run_all.py against live sandboxes, then scripts/build_workbook.py, to populate these rows.</t>
+          <t>Empty by design. Run benchmarks in BuraPay against live sandboxes, then scripts/build_workbook.py, to populate these rows.</t>
         </is>
       </c>
     </row>
